--- a/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Test_Cases_and_Results.xlsx
+++ b/Capstone_Project/06_Testing_Results_and_Evaluation/Group-3_Test_Cases_and_Results.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tracker" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$3:$L$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Tracker'!$A$3:$K$103</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -89,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,7 +98,10 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -467,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="1"/>
@@ -479,9 +481,9 @@
     <col width="35" customWidth="1" style="4" min="7" max="8"/>
     <col width="55" customWidth="1" style="4" min="8" max="8"/>
     <col width="14" customWidth="1" style="4" min="9" max="9"/>
-    <col width="18" customWidth="1" style="4" min="10" max="10"/>
-    <col width="14" customWidth="1" style="4" min="11" max="11"/>
-    <col width="28" customWidth="1" style="4" min="12" max="12"/>
+    <col width="14" customWidth="1" style="4" min="10" max="10"/>
+    <col width="28" customWidth="1" style="4" min="11" max="11"/>
+    <col width="13" customWidth="1" style="4" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" customHeight="1" s="4">
@@ -491,6 +493,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -539,15 +542,10 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
@@ -599,15 +597,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="J4" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -659,15 +652,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="J5" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -719,15 +707,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="J6" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -779,15 +762,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="J7" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -839,15 +817,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="J8" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -899,15 +872,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="J9" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -959,15 +927,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="J10" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1019,15 +982,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="J11" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js and server log</t>
         </is>
@@ -1079,15 +1037,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="J12" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1139,15 +1092,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="J13" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1191,7 +1139,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Scripted run on a phone screen took 1.8 seconds from login to the confirmation. The timed task with real students is planned for Week 5 user testing</t>
+          <t>Scripted run on a phone screen took 1.9 seconds from login to the confirmation. The timed task with real students is planned for Week 5 user testing</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1199,15 +1147,10 @@
           <t>Not Run</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="J14" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js and Week 5 user testing</t>
         </is>
@@ -1251,7 +1194,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>phone: login 84 ms book after login 270 ms my bookings 452 ms; laptop: login 78 ms book after login 287 ms my bookings 378 ms</t>
+          <t>phone: login 127 ms book after login 305 ms my bookings 382 ms; laptop: login 82 ms book after login 218 ms my bookings 387 ms</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1259,15 +1202,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
+      <c r="J15" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js</t>
         </is>
@@ -1319,15 +1257,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="J16" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js and evidence screenshots</t>
         </is>
@@ -1379,15 +1312,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="J17" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1439,15 +1367,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="J18" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1499,15 +1422,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="J19" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1559,15 +1477,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="J20" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1611,7 +1524,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>wrong password message "Wrong email or password please try again" and email kept "willem.gerber@campusbook.test"; empty form message "Enter your email address and your password."; slot taken message "Sorry that slot is no longer available" ; the reason box was hidden after the error: true; after choosing another time the reason box still holds "My typed reason should stay"</t>
+          <t>Before the fixes: after a failed booking the reason box was hidden and the confirm step had to be started again (D-08). After the fixes: wrong password message "Wrong email or password please try again" and email kept "willem.gerber@campusbook.test"; empty form message "Enter your email address and your password."; slot taken message "Sorry that slot is no longer available" ; the reason box was hidden after the error: true; after choosing another time the reason box still holds "My typed reason should stay"</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1619,15 +1532,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
+      <c r="J21" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js</t>
         </is>
@@ -1679,15 +1587,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="J22" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1739,15 +1642,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
+      <c r="J23" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1799,15 +1697,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="J24" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1859,15 +1752,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="J25" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1919,15 +1807,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="J26" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -1979,15 +1862,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="J27" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -2039,15 +1917,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="J28" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -2091,7 +1964,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20 requests: median 3 ms slowest 19 ms</t>
+          <t>20 requests: median 6 ms slowest 21 ms</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2099,15 +1972,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="J29" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -2126,50 +1994,45 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Lecturer slots page</t>
+          <t>Lecturer publishes a slot from the page</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Lecturer account</t>
+          <t>Lecturer account and the Lecturer slots page</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1 Log in as a lecturer 2 Read the page at /lecturer/slots</t>
+          <t>1 Log in as a lecturer 2 Read the slot list on /lecturer/slots 3 Fill the form and press Publish slot</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>jabulile.mashibini@campusbook.test</t>
+          <t>jabulile.mashibini@campusbook.test and a slot 5 days ahead from 14:00 to 14:30</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Page shows the lecturer slots and a form to publish a slot</t>
+          <t>The page lists the lecturer slots and publishing saves the slot</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>After lecturer login the page at /lecturer/slots shows: "CampusBook My slots JM Jabulile Mashibini Lecturer Log out My consultation slots This page is coming soon."</t>
+          <t>Before the fixes (commit e9ab578): the list failed with "That API route does not exist" because the page called GET /api/slots/my and the route is /api/slots/mine and publishing showed "Enter a valid start time (HH:MM) Enter a valid end time (HH:MM)" because the page sent start and end and the API needs startTime and endTime and nothing was saved. After the fixes: the list shows the slots and publishing returns 201 and the slot is saved</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>test_scripts/ui_tests.js and laptop_lecturer.png</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>test_scripts/lect_tests.js and evidence lecturer_before_laptop.png and lecturer_after_laptop.png</t>
         </is>
       </c>
     </row>
@@ -2219,15 +2082,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="J31" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -2266,12 +2124,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Visitors go to login and each role is kept off the other roles pages</t>
+          <t>Visitors go to login and each role is sent to their own home page</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>not logged in opening /book goes to /login; student opening /lecturer/slots goes to /login; lecturer opening /book goes to /login</t>
+          <t>Before the fixes: a student or lecturer opening the other roles page was sent to the login page (D-09). After the fixes: not logged in opening /book goes to /login; student opening /lecturer/slots goes to /book; lecturer opening /book goes to /lecturer/slots</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2279,15 +2137,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
+      <c r="J32" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js</t>
         </is>
@@ -2331,23 +2184,18 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>after the token became invalid the page stayed at /my-bookings and showed "Your session has expired please log in again"</t>
+          <t>Before the fixes: the user stayed on the page with an error and the old token was kept (D-05). After the fixes: after the token became invalid the page stayed at /login and showed "Your session has ended. Please log in again."</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>test_scripts/ui_tests.js and laptop_expired.png</t>
         </is>
@@ -2376,40 +2224,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1 Open my bookings 2 Look for a change button</t>
+          <t>1 Open my bookings 2 Look for a change button 3 Change the booking to another time</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>oscar.khumalo@campusbook.test</t>
+          <t>willem.gerber@campusbook.test</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>A change button is offered next to cancel</t>
+          <t>A change button is offered next to cancel and moving the booking works</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>buttons on the booking rows: ["Cancel booking"]</t>
+          <t>Before the fixes: only a Cancel booking button was offered (D-04). After the fixes: buttons on the booking rows: ["Change time""Cancel booking"] and moving the booking showed the notice Your booking has moved and the lecturer has been told</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>test_scripts/ui_tests.js</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>test_scripts/extras_tests.js and ui_tests.js</t>
         </is>
       </c>
     </row>
@@ -2436,7 +2279,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1 Send 40 wrong passwords for one account 2 Then send the correct password</t>
+          <t>1 Send wrong passwords for one account 2 Then send the correct password for another account</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2446,30 +2289,25 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>The attempts are slowed or blocked after several failures</t>
+          <t>The attempts are blocked after several failures and other accounts are not affected</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>All 40 wrong passwords were answered with 401 and no limit applied. The correct login then worked with 200</t>
+          <t>Before the fixes: all 40 wrong passwords were answered with 401 and no limit applied. After the fixes: the first 10 wrong passwords gave 401 and the next 2 gave 429 Too many failed attempts and another account still logged in with 200</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>Server log and login route</t>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>test_scripts/extras_tests.js (D-06)</t>
         </is>
       </c>
     </row>
@@ -2519,15 +2357,10 @@
           <t>Pass</t>
         </is>
       </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
+      <c r="J36" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
         <is>
           <t>test_scripts/api_tests.js</t>
         </is>
@@ -2551,7 +2384,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Main branch at commit 1cfc84c</t>
+          <t>Main branch at commit e9ab578</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2571,55 +2404,132 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Buttons showed only "to" and the confirm panel showed "undefined to undefined". Retest with the fix in the test copy: buttons show 09:00 to 09:30 and 09:30 to 10:00</t>
+          <t>Before the fix: buttons showed only "to" and the confirm panel showed "undefined to undefined". After the fix: buttons show 09:00 to 09:30 and 09:30 to 10:00</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>46317</v>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
         <is>
           <t>times_before.png and times_after.png</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n"/>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
-      <c r="G38" s="2" t="n"/>
-      <c r="H38" s="2" t="n"/>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="2" t="n"/>
-      <c r="L38" s="2" t="n"/>
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>TC-33</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer removes a slot from the page</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer account and the Lecturer slots page</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1 Open /lecturer/slots 2 Press Remove on a slot and confirm</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>An open slot of lecturer 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>The slot is removed and the list updates</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Before the fixes: blocked because the list never loaded so there was no slot to remove. After the fixes: the notice Consultation slot removed shows and the row leaves the list (DELETE returned 200)</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>test_scripts/lect_tests.js</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>FR-03</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer edits a slot from the page</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Lecturer account and the Lecturer slots page</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1 Open /lecturer/slots 2 Press Edit on a slot 3 Change the location and press Save changes</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Location changed to Room C3</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>The page offers an edit option and the change is saved</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Before the fixes: the page only had a Remove button and no edit option although the API supports editing with PUT /api/slots/:id (D-10). After the fixes: Edit fills the form and Save changes shows Consultation slot updated and the database holds the new location (PUT returned 200)</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>test_scripts/lect_tests.js and lecturer_edit_laptop.png</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n"/>
@@ -2633,7 +2543,6 @@
       <c r="I40" s="2" t="n"/>
       <c r="J40" s="2" t="n"/>
       <c r="K40" s="2" t="n"/>
-      <c r="L40" s="2" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -2647,7 +2556,6 @@
       <c r="I41" s="2" t="n"/>
       <c r="J41" s="2" t="n"/>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n"/>
@@ -2661,7 +2569,6 @@
       <c r="I42" s="2" t="n"/>
       <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -2675,7 +2582,6 @@
       <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
-      <c r="L43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -2689,7 +2595,6 @@
       <c r="I44" s="2" t="n"/>
       <c r="J44" s="2" t="n"/>
       <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -2703,7 +2608,6 @@
       <c r="I45" s="2" t="n"/>
       <c r="J45" s="2" t="n"/>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -2717,7 +2621,6 @@
       <c r="I46" s="2" t="n"/>
       <c r="J46" s="2" t="n"/>
       <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -2731,7 +2634,6 @@
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -2745,7 +2647,6 @@
       <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -2759,7 +2660,6 @@
       <c r="I49" s="2" t="n"/>
       <c r="J49" s="2" t="n"/>
       <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -2773,7 +2673,6 @@
       <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -2787,7 +2686,6 @@
       <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -2801,7 +2699,6 @@
       <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -2815,12 +2712,11 @@
       <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
-      <c r="L53" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:L103"/>
+  <autoFilter ref="A3:K103"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I4:I53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
